--- a/g4-texas-ss-image-manifest.xlsx
+++ b/g4-texas-ss-image-manifest.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1695,6 +1695,924 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ss-tx-4-3.05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3 Spanish Colonial Texas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Government in Spanish Texas</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Spanish Colonial Government Hierarchy</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Historical Diagram</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>source-4-03-05-colonial-hierarchy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>source-4-03-05-colonial-hierarchy.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Diagram showing the hierarchy of Spanish colonial government: King of Spain → Council of the Indies → Viceroy of New Spain → Provincial Governor → Local Officials, with brief labels for each role.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ss-tx-4-3.06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3 Spanish Colonial Texas</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Effects of Colonial Rule</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Colonial Rules for Mission Life</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Historical Recreation</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>source-4-03-06-mission-daily-schedule</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>source-4-03-06-mission-daily-schedule.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>A recreation of a typical daily schedule at a Spanish mission in Texas, showing wake-up bells, prayer times, work hours, meals, and evening devotions.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ss-tx-4-3.07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3 Spanish Colonial Texas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Mexican Independence and Texas</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Timeline of Mexican Independence</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Historical Timeline</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>source-4-03-07-mexican-independence-timeline</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>source-4-03-07-mexican-independence-timeline.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Illustrated timeline from 1810-1821 showing key events of Mexican independence: Grito de Dolores, Hidalgo's campaign, Morelos, and Iturbide's entry into Mexico City.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ss-tx-4-3.08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3 Spanish Colonial Texas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Texas Under New Rule</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Texas Under Spanish vs. Mexican Rule</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Comparison Chart</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>source-4-03-08-spanish-vs-mexican-rule</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>source-4-03-08-spanish-vs-mexican-rule.jpg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Side-by-side comparison chart of life in Texas under Spanish rule vs. Mexican rule, covering government, religion, trade, land policy, and immigration.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Empresarios: Austin and de León</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Empresario Land Grant Contract</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Historical Document</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>source-4-04-01-empresario-land-grant</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>source-4-04-01-empresario-land-grant.jpg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Recreation of an empresario land grant contract showing terms, acreage, settler requirements (Catholic, loyal to Mexico), and signatures.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.02</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Building Colonial Communities</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Early Colony Settlement</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Historical Map/Sketch</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>source-4-04-02-san-felipe-sketch</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>source-4-04-02-san-felipe-sketch.jpg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sketch or early map of San Felipe de Austin showing the layout of the town, the Brazos River, and surrounding farmland.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Settlement Geography</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Empresario Colonies Map</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Historical Map</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>source-4-04-03-empresario-colonies-map</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>source-4-04-03-empresario-colonies-map.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Map of Texas showing the major empresario land grants (Austin, de León, DeWitt, and others) along rivers and coastal areas.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Free Enterprise in Early Texas</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Early Texas Trade Goods</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Historical Recreation</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>source-4-04-04-trade-goods-ledger</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>source-4-04-04-trade-goods-ledger.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Recreation of a frontier trading post ledger or inventory showing goods bought and sold: cotton, cattle, corn, tools, cloth, and prices.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Growing Tensions</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Law of April 6, 1830</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Historical Document</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>source-4-04-05-law-april-1830</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>source-4-04-05-law-april-1830.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Excerpt or broadside-style recreation of key provisions of the Law of April 6, 1830, restricting American immigration and imposing customs duties.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ss-tx-4-4.06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4 Mexican Texas and Colonization</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Voices Before Revolution</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Austin's Letter from Prison</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Primary Source Letter</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>source-4-04-06-austin-prison-letter</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>source-4-04-06-austin-prison-letter.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Excerpt from Stephen F. Austin's letter written during his imprisonment in Mexico City (1834), expressing frustration and shifting views on independence.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>The Revolution Begins</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Come and Take It Flag</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Historical Artifact</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>source-4-05-01-come-and-take-it</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>source-4-05-01-come-and-take-it.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The 'Come and Take It' flag from the Battle of Gonzales (1835), showing a cannon and lone star with the defiant phrase.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.02</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The Texas Declaration of Independence</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Texas Declaration of Independence</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Primary Source Document</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>source-4-05-02-texas-declaration</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>source-4-05-02-texas-declaration.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The Texas Declaration of Independence document (1836), showing the parchment with key grievances and signatures of the 59 delegates.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The Alamo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Artistic Depiction of the Alamo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Historical Painting</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>source-4-05-03-alamo-painting</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>source-4-05-03-alamo-painting.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A painting or artistic depiction of the Battle of the Alamo — to be analyzed as 'art as evidence' (what does the artist emphasize vs. what is missing?).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Siege Sources and Perspectives</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Travis's Victory or Death Letter</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Primary Source Letter</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>source-4-05-04-travis-letter</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>source-4-05-04-travis-letter.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>William Barret Travis's 'Victory or Death' letter from the Alamo (February 24, 1836), appealing for reinforcements.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>The Runaway Scrape</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Runaway Scrape Routes Map</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Historical Map</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>source-4-05-05-runaway-scrape-map</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>source-4-05-05-runaway-scrape-map.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Map showing the routes Texas civilians took fleeing eastward during the Runaway Scrape (March-April 1836), with rivers, mud, and key locations marked.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>San Jacinto: The Turning Point</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Battle of San Jacinto Map</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Battle Map</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>source-4-05-06-san-jacinto-battle-map</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>source-4-05-06-san-jacinto-battle-map.jpg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Battle map of San Jacinto showing troop positions of Houston's Texian army and Santa Anna's Mexican forces, Buffalo Bayou, and the attack route.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Birth of the Republic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Republic of Texas Flag and Government</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Historical Artifact</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>source-4-05-07-republic-flag</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>source-4-05-07-republic-flag.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The Lone Star flag of the Republic of Texas alongside a diagram of the new republic's government structure (president, congress, courts).</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ss-tx-4-5.08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5 Texas Revolution and Independence</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Q2 Exhibition: Revolution to Republic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Q2 Composite Sources</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Student Selection</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>source-4-05-08-q2-exhibition</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>source-4-05-08-q2-exhibition.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Composite image representing key sources studied in Q2: colonial documents, empresario maps, revolution artifacts, and republic symbols.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Needed</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K23"/>
